--- a/diseases/d212/2026-2029.xlsx
+++ b/diseases/d212/2026-2029.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10264,6 +10264,405 @@
         </is>
       </c>
       <c r="BC49" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>围产期丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>围产期丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Hepatitis C, perinatal, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Confirmed perinatal hepatitis C series.</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -10302,7 +10701,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -10385,7 +10784,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -10395,7 +10794,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -10415,7 +10814,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -10447,7 +10846,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d212/2026-2029.xlsx
+++ b/diseases/d212/2026-2029.xlsx
@@ -10668,6 +10668,405 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>围产期丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>围产期丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Hepatitis C, perinatal, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Confirmed perinatal hepatitis C series.</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10701,7 +11100,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -10784,7 +11183,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -10794,7 +11193,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -10814,7 +11213,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -10846,7 +11245,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d212/2026-2029.xlsx
+++ b/diseases/d212/2026-2029.xlsx
@@ -11067,6 +11067,405 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>围产期丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>2</v>
+      </c>
+      <c r="O54" t="n">
+        <v>2</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>围产期丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Hepatitis C, perinatal, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Confirmed perinatal hepatitis C series.</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11100,7 +11499,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11582,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -11193,7 +11592,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -11213,7 +11612,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -11245,7 +11644,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d212/2026-2029.xlsx
+++ b/diseases/d212/2026-2029.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -11461,6 +11461,405 @@
         </is>
       </c>
       <c r="BC55" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>围产期丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>2</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>perinatal-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D212</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Perinatal hepatitis C</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>围产期丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>2</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Hepatitis C, perinatal, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Confirmed perinatal hepatitis C series.</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_US_PERINATAL_HEPATITIS_C</t>
+        </is>
+      </c>
+      <c r="AT57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -11499,7 +11898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11981,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -11592,7 +11991,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -11612,7 +12011,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -11644,7 +12043,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d212/2026-2029.xlsx
+++ b/diseases/d212/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -793,12 +788,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -808,11 +798,6 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -933,11 +918,6 @@
       <c r="R3" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -955,12 +935,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -970,11 +945,6 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1095,11 +1065,6 @@
       <c r="R4" t="n">
         <v>0.001146015253107754</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -1117,12 +1082,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1132,11 +1092,6 @@
       </c>
       <c r="AT4" t="n">
         <v>1</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1257,11 +1212,6 @@
       <c r="R5" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -1279,12 +1229,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1294,11 +1239,6 @@
       </c>
       <c r="AT5" t="n">
         <v>1</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1419,11 +1359,6 @@
       <c r="R6" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -1441,12 +1376,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1456,11 +1386,6 @@
       </c>
       <c r="AT6" t="n">
         <v>1</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1581,11 +1506,6 @@
       <c r="R7" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -1603,12 +1523,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1618,11 +1533,6 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1743,11 +1653,6 @@
       <c r="R8" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -1765,12 +1670,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1780,11 +1680,6 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1905,11 +1800,6 @@
       <c r="R9" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -1927,12 +1817,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1942,11 +1827,6 @@
       </c>
       <c r="AT9" t="n">
         <v>1</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2067,11 +1947,6 @@
       <c r="R10" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -2089,12 +1964,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2104,11 +1974,6 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2229,11 +2094,6 @@
       <c r="R11" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -2251,12 +2111,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2266,11 +2121,6 @@
       </c>
       <c r="AT11" t="n">
         <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2391,11 +2241,6 @@
       <c r="R12" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -2413,12 +2258,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2428,11 +2268,6 @@
       </c>
       <c r="AT12" t="n">
         <v>1</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2553,11 +2388,6 @@
       <c r="R13" t="n">
         <v>0.001146015253107754</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -2575,12 +2405,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2590,11 +2415,6 @@
       </c>
       <c r="AT13" t="n">
         <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2715,11 +2535,6 @@
       <c r="R14" t="n">
         <v>0.0008595114398308156</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -2737,12 +2552,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2752,11 +2562,6 @@
       </c>
       <c r="AT14" t="n">
         <v>1</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2877,11 +2682,6 @@
       <c r="R15" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -2899,12 +2699,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2914,11 +2709,6 @@
       </c>
       <c r="AT15" t="n">
         <v>1</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3039,11 +2829,6 @@
       <c r="R16" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -3061,12 +2846,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3076,11 +2856,6 @@
       </c>
       <c r="AT16" t="n">
         <v>1</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3201,11 +2976,6 @@
       <c r="R17" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -3223,12 +2993,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3238,11 +3003,6 @@
       </c>
       <c r="AT17" t="n">
         <v>1</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3363,11 +3123,6 @@
       <c r="R18" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -3385,12 +3140,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -3400,11 +3150,6 @@
       </c>
       <c r="AT18" t="n">
         <v>1</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3525,11 +3270,6 @@
       <c r="R19" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -3547,12 +3287,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3562,11 +3297,6 @@
       </c>
       <c r="AT19" t="n">
         <v>1</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3687,11 +3417,6 @@
       <c r="R20" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -3709,12 +3434,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -3724,11 +3444,6 @@
       </c>
       <c r="AT20" t="n">
         <v>1</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3849,11 +3564,6 @@
       <c r="R21" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -3871,12 +3581,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -3886,11 +3591,6 @@
       </c>
       <c r="AT21" t="n">
         <v>1</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -4011,11 +3711,6 @@
       <c r="R22" t="n">
         <v>0.0008595114398308156</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -4033,12 +3728,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -4048,11 +3738,6 @@
       </c>
       <c r="AT22" t="n">
         <v>1</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4173,11 +3858,6 @@
       <c r="R23" t="n">
         <v>0.0008595114398308156</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -4195,12 +3875,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -4210,11 +3885,6 @@
       </c>
       <c r="AT23" t="n">
         <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4335,11 +4005,6 @@
       <c r="R24" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -4357,12 +4022,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -4372,11 +4032,6 @@
       </c>
       <c r="AT24" t="n">
         <v>1</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4497,11 +4152,6 @@
       <c r="R25" t="n">
         <v>0.0008595114398308156</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -4519,12 +4169,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -4534,11 +4179,6 @@
       </c>
       <c r="AT25" t="n">
         <v>1</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4659,11 +4299,6 @@
       <c r="R26" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -4681,12 +4316,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4696,11 +4326,6 @@
       </c>
       <c r="AT26" t="n">
         <v>1</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4821,11 +4446,6 @@
       <c r="R27" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -4843,12 +4463,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -4858,11 +4473,6 @@
       </c>
       <c r="AT27" t="n">
         <v>1</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4983,11 +4593,6 @@
       <c r="R28" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -5005,12 +4610,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -5020,11 +4620,6 @@
       </c>
       <c r="AT28" t="n">
         <v>1</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5145,11 +4740,6 @@
       <c r="R29" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>HOLD_US_711ab9679015706ab1ed860d0a5b</t>
@@ -5167,12 +4757,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -5182,11 +4767,6 @@
       </c>
       <c r="AT29" t="n">
         <v>1</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
